--- a/outputs/hard_cheese/novus/primary_chain_output.xlsx
+++ b/outputs/hard_cheese/novus/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001649183941800067</v>
+        <v>0.001649183941799371</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
       </c>
       <c r="D2" t="n">
-        <v>1.66813437649029e-12</v>
+        <v>1.668134376491154e-12</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>4.160589056408487e-21</v>
+        <v>4.160589056408666e-21</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -574,13 +574,13 @@
         <v>0.08893253878307611</v>
       </c>
       <c r="D3" t="n">
-        <v>1.532473806067052e-08</v>
+        <v>1.532473806066898e-08</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.196556730323243e-10</v>
+        <v>1.196556730322677e-10</v>
       </c>
       <c r="G3" t="n">
         <v>0.04166666666668085</v>
@@ -630,7 +630,7 @@
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>9.880315207497819e-05</v>
+        <v>9.880315207498014e-05</v>
       </c>
       <c r="G4" t="n">
         <v>0.1</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.2322700832601339</v>
+        <v>0.232270083260134</v>
       </c>
       <c r="N5" t="n">
         <v>189</v>
@@ -942,22 +942,22 @@
         <v>187</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.901684280673745</v>
+        <v>-1.901684280673758</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3195396559542991</v>
+        <v>0.3195396559542992</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.703887241265392</v>
+        <v>-0.7038872412653931</v>
       </c>
       <c r="M2" t="n">
-        <v>2.747609431022365e-15</v>
+        <v>2.747609431018937e-15</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1625343111972001</v>
+        <v>0.1625343111971972</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2610022514748195</v>
+        <v>0.2610022514748128</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3045392670214256</v>
+        <v>0.3045392670214253</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2688968463348229</v>
+        <v>0.2688968463348201</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05424410826903407</v>
+        <v>0.05424410826903467</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -57055,10 +57055,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.852886918113318</v>
+        <v>-1.852886918113325</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04879736256042733</v>
+        <v>0.04879736256043321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -57071,10 +57071,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.52011630994642</v>
+        <v>-1.520116309946426</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04003356383238164</v>
+        <v>0.04003356383238646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -57087,10 +57087,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.579880495540932</v>
+        <v>-1.579880495540938</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04160750480205159</v>
+        <v>0.04160750480205661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -57103,10 +57103,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.56914710204969</v>
+        <v>-1.569147102049695</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04132483169956718</v>
+        <v>0.04132483169957216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -57119,10 +57119,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.571074773860019</v>
+        <v>-1.571074773860025</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04137559858625983</v>
+        <v>0.04137559858626482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -57135,10 +57135,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.570728572203351</v>
+        <v>-1.570728572203357</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04136648106937615</v>
+        <v>0.04136648106938114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -57151,10 +57151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.57079074854812</v>
+        <v>-1.570790748548125</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04136811853662183</v>
+        <v>0.04136811853662681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -57167,10 +57167,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.570779581941102</v>
+        <v>-1.570779581941108</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04136782445447042</v>
+        <v>0.04136782445447541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -57183,10 +57183,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.570781587416219</v>
+        <v>-1.570781587416225</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04136787727037376</v>
+        <v>0.04136787727037875</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -57199,10 +57199,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.57078122724142</v>
+        <v>-1.570781227241425</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04136786778486221</v>
+        <v>0.04136786778486719</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -57215,10 +57215,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.570781291927281</v>
+        <v>-1.570781291927287</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04136786948841973</v>
+        <v>0.04136786948842472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -57231,10 +57231,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.570781280309976</v>
+        <v>-1.570781280309981</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04136786918246804</v>
+        <v>0.04136786918247303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57247,10 +57247,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.570781282396394</v>
+        <v>-1.5707812823964</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04136786923741567</v>
+        <v>0.04136786923742065</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -57263,10 +57263,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.570781282021682</v>
+        <v>-1.570781282021688</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04136786922754731</v>
+        <v>0.04136786922755229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -57279,10 +57279,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.570781282088979</v>
+        <v>-1.570781282088985</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04136786922931962</v>
+        <v>0.04136786922932461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -57295,10 +57295,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.570781282076893</v>
+        <v>-1.570781282076898</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04136786922900132</v>
+        <v>0.04136786922900631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -57311,10 +57311,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.570781282079064</v>
+        <v>-1.570781282079069</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04136786922905849</v>
+        <v>0.04136786922906347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -57327,10 +57327,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.570781282078674</v>
+        <v>-1.570781282078679</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04136786922904822</v>
+        <v>0.04136786922905321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -57343,10 +57343,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.570781282078744</v>
+        <v>-1.570781282078749</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04136786922905007</v>
+        <v>0.04136786922905505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -57359,10 +57359,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.570781282078731</v>
+        <v>-1.570781282078737</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04136786922904973</v>
+        <v>0.04136786922905472</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -57375,10 +57375,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.570781282078733</v>
+        <v>-1.570781282078739</v>
       </c>
       <c r="C22" t="n">
-        <v>0.04136786922904979</v>
+        <v>0.04136786922905478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
